--- a/Evaluation/proposed_responses.xlsx
+++ b/Evaluation/proposed_responses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manaranjanp/Documents/Work/LLM/Draft Course/notebooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manaranjanp/Documents/Work/Consulting/Intuit/RAG/github/RAG2Days/Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278B337C-1130-654D-B6E9-9F7C49B0ADD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE3055F-3FE0-1444-89D7-B9C6CEF7FC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17140" xr2:uid="{1CA7A62D-8352-0144-8309-66628DA85E10}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{1CA7A62D-8352-0144-8309-66628DA85E10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -425,8 +425,8 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81" style="1" customWidth="1"/>
+    <col min="1" max="1" width="91" style="1" customWidth="1"/>
+    <col min="2" max="2" width="119.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="74.83203125" customWidth="1"/>
   </cols>
   <sheetData>
